--- a/Agent Bank Summary.xlsx
+++ b/Agent Bank Summary.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Agent Bank Summary" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Agent Bank Summary" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="BB Templates" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="262">
   <si>
     <t xml:space="preserve">Agent</t>
   </si>
@@ -497,6 +498,441 @@
   </si>
   <si>
     <t xml:space="preserve">Totals Loan Amount1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KKR Ascendant Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One tab (Borrowing Base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Row 2: Title: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KKR Ascendant – Borrowing Base</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Fund Sleeve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows 3-9: Summaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moody’s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 10: Column Headers (listed in next column)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S&amp;P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Rated Included Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Worth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Non-Rated Included Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Designated Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funded Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Borrowing Base Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unfunded Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Hurdle Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Total Unfunded Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Excluded Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentration Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eligible Unfunded Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advance Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrowing Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audax Fund VII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicon Valley Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple tabs (Investor List)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferred From</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 4: Deal Name: Nerdio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 9-10: Borrowers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrowing Partnership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column 13: Column Headers (listed in next column)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Header Columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included/Excluded Investor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital Commitments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Included Unfunded Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excess Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-CL Unfunded Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Adjustment Borrowing Base Contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrowing Base Adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCP VII Lev M &amp; M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor Name</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Row 3: Title: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comvest Credit Partners VII, LP.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 7: Column Headers (listed in next column)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defaulting?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Levered (Delaware) Feeder, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claimed/Exercised Rights?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: (Cayman) Feeder, L.P., followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Committed Capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: (Delaware) Feeder, L.P., followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recallable Distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Lux Intermediate, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining Callable Capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Lux Non-Treaty Feeder, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AEP VII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One tab (BB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Shading: LPs new to the BB not via LP Transfer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Line 2: Title: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AURORA EQUITY PARTNERS VII LP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow Shading: LPs new to the BB via LP Transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 3-9: Summaries </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue Text: LPs with a change in Commitment Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 11: Column Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underlined Text: LPs with a change in Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: Non-Rated Included Investors, followed by a subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP VII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple tabs (BB)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Row 83: Title: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Carlyle Partners VII</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Capital Commitments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 84-85: Column Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of Eligible Commitments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of All Commitments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contributions Called to Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excess Concentration %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eligible Contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue Owl GP Stakes V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple tabs (Agent BB)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Row 2: Title: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Blue Owl GP Stakes V – Subscription Facility Borrowing Base</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent / Sponsor / Manager</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rose Background: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Reclassified</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows 3-17: Summary tables</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Light Turquoise Background: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Transferee</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 18: Column Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: A. Rated Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Assets (range)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: B. Unrated Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual Original Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: C. Eligible Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Column: D. Excluded Investors, followed by subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual Unfunded Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unfunded Capital Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Called</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Eligible Unfunded Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eligible Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrowing Base Contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of Borrowing Base</t>
   </si>
 </sst>
 </file>
@@ -508,11 +944,12 @@
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -534,14 +971,53 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A6099"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF729FCF"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -578,40 +1054,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -624,7 +1132,173 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF729FCF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFF7D1D5"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF00A933"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -633,1730 +1307,1730 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G105"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="26.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="21.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="21.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>46321</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>46163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>87500000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>46528</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>46129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="0" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>300000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>46521</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>46136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="0" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>67829457</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>46450</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>46114</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="0" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>46764</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>46155</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="B8" s="0" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>112000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>46589</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>45861</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="0" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>92000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>46367</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>46158</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="0" t="s">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>112000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>46589</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="3" t="n">
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>45861</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>300000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>46640</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>45917</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="0" t="s">
+      <c r="A12" s="5"/>
+      <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>135000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>46521</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="F12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>46158</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4"/>
-      <c r="B13" s="0" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>73076924</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>46492</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="3" t="n">
+      <c r="F13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>46129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="0" t="s">
+      <c r="A14" s="5"/>
+      <c r="B14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>45000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>46402</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="F14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>46184</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="0" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>46633</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="F15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>45906</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4"/>
-      <c r="B16" s="0" t="s">
+      <c r="A16" s="5"/>
+      <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>46619</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>45890</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="0" t="s">
+      <c r="A17" s="5"/>
+      <c r="B17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>300000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>46832</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="F17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>46156</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4"/>
-      <c r="B18" s="0" t="s">
+      <c r="A18" s="5"/>
+      <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>47025</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="3" t="n">
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>46056</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4"/>
-      <c r="C19" s="5" t="s">
+      <c r="A19" s="5"/>
+      <c r="C19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <f aca="false">SUM(D3:D18)</f>
         <v>2224406381</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="0" t="s">
+      <c r="A21" s="5"/>
+      <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="3" t="n">
         <v>200000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="F21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>46088</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4"/>
-      <c r="B22" s="0" t="s">
+      <c r="A22" s="5"/>
+      <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="3" t="n">
         <v>132500000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>46380</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="F22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>45987</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4"/>
-      <c r="C23" s="5" t="s">
+      <c r="A23" s="5"/>
+      <c r="C23" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <f aca="false">SUM(D21, D22)</f>
         <v>332500000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <v>150000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>46395</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="3" t="n">
+      <c r="F25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>46023</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <f aca="false">SUM(D25)</f>
         <v>150000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="0" t="s">
+      <c r="A28" s="5"/>
+      <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="3" t="n">
         <v>165000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>46533</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="3" t="n">
+      <c r="F28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>46162</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4"/>
-      <c r="C29" s="5" t="s">
+      <c r="A29" s="5"/>
+      <c r="C29" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <f aca="false">SUM($D28)</f>
         <v>165000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4"/>
-      <c r="B31" s="0" t="s">
+      <c r="A31" s="5"/>
+      <c r="B31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="3" t="n">
         <v>125000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>46274</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="3" t="n">
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="4" t="n">
         <v>46024</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4"/>
-      <c r="C32" s="5" t="s">
+      <c r="A32" s="5"/>
+      <c r="C32" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <f aca="false">SUM($D31)</f>
         <v>125000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4"/>
-      <c r="B34" s="0" t="s">
+      <c r="A34" s="5"/>
+      <c r="B34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="3" t="n">
         <v>213157895</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>46209</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="3" t="n">
+      <c r="F34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="4" t="n">
         <v>46142</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4"/>
-      <c r="B35" s="0" t="s">
+      <c r="A35" s="5"/>
+      <c r="B35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>46668</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="3" t="n">
+      <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="4" t="n">
         <v>45941</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
-      <c r="B36" s="0" t="s">
+      <c r="A36" s="5"/>
+      <c r="B36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="3" t="n">
         <v>140000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>46262</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="F36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4" t="n">
         <v>45898</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4"/>
-      <c r="B37" s="0" t="s">
+      <c r="A37" s="5"/>
+      <c r="B37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="3" t="n">
+      <c r="F37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>45890</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4"/>
-      <c r="B38" s="0" t="s">
+      <c r="A38" s="5"/>
+      <c r="B38" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>44200000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>46195</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="4" t="n">
         <v>46119</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4"/>
-      <c r="B39" s="0" t="s">
+      <c r="A39" s="5"/>
+      <c r="B39" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>200000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>46498</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="3" t="n">
+      <c r="F39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4" t="n">
         <v>46143</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4"/>
-      <c r="C40" s="5" t="s">
+      <c r="A40" s="5"/>
+      <c r="C40" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="7" t="n">
         <f aca="false">SUM(D34:D39)</f>
         <v>947357895</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
-      <c r="B42" s="0" t="s">
+      <c r="A42" s="5"/>
+      <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>99525317</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4"/>
-      <c r="C43" s="5" t="s">
+      <c r="A43" s="5"/>
+      <c r="C43" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="7" t="n">
         <f aca="false">SUM(D42)</f>
         <v>99525317</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>46458</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="3" t="n">
+      <c r="F43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="4" t="n">
         <v>46102</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4"/>
-      <c r="B45" s="0" t="s">
+      <c r="A45" s="5"/>
+      <c r="B45" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>165000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>46339</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="3" t="n">
+      <c r="F45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="4" t="n">
         <v>45905</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4"/>
-      <c r="C46" s="5" t="s">
+      <c r="A46" s="5"/>
+      <c r="C46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="7" t="n">
         <f aca="false">SUM(D45)</f>
         <v>165000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4"/>
-      <c r="B48" s="0" t="s">
+      <c r="A48" s="5"/>
+      <c r="B48" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="3" t="n">
         <v>200000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="4" t="n">
         <v>46934</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="3" t="n">
+      <c r="F48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="4" t="n">
         <v>46127</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4"/>
-      <c r="B49" s="0" t="s">
+      <c r="A49" s="5"/>
+      <c r="B49" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>170000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="4" t="n">
         <v>46477</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="3" t="n">
+      <c r="F49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="4" t="n">
         <v>46114</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4"/>
-      <c r="C50" s="5" t="s">
+      <c r="A50" s="5"/>
+      <c r="C50" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="7" t="n">
         <f aca="false">SUM(D48:D49)</f>
         <v>370000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4"/>
-      <c r="B52" s="0" t="s">
+      <c r="A52" s="5"/>
+      <c r="B52" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="3" t="n">
         <v>240000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="4" t="n">
         <v>46304</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" s="3" t="n">
+      <c r="F52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="4" t="n">
         <v>46037</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4"/>
-      <c r="B53" s="0" t="s">
+      <c r="A53" s="5"/>
+      <c r="B53" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>138000000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G53" s="3" t="n">
+      <c r="F53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="4" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4"/>
-      <c r="B54" s="0" t="s">
+      <c r="A54" s="5"/>
+      <c r="B54" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="3" t="n">
         <v>143285718</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="4" t="n">
         <v>46238</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="3" t="n">
+      <c r="F54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="4" t="n">
         <v>45870</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4"/>
-      <c r="B55" s="0" t="s">
+      <c r="A55" s="5"/>
+      <c r="B55" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>156250000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G55" s="3" t="n">
+      <c r="F55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="4" t="n">
         <v>46126</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4"/>
-      <c r="C56" s="5" t="s">
+      <c r="A56" s="5"/>
+      <c r="C56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="7" t="n">
         <f aca="false">SUM(D52:D55)</f>
         <v>677535718</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4"/>
-      <c r="B58" s="0" t="s">
+      <c r="A58" s="5"/>
+      <c r="B58" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="3" t="n">
         <v>292050000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="4" t="n">
         <v>46197</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" s="3" t="n">
+      <c r="F58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="4" t="n">
         <v>45833</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4"/>
-      <c r="B59" s="0" t="s">
+      <c r="A59" s="5"/>
+      <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="3" t="n">
         <v>7950000</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="4" t="n">
         <v>46197</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G59" s="3" t="n">
+      <c r="F59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="4" t="n">
         <v>45833</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4"/>
-      <c r="C60" s="5" t="s">
+      <c r="A60" s="5"/>
+      <c r="C60" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" s="7" t="n">
         <f aca="false">SUM(D58:D59)</f>
         <v>300000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4"/>
-      <c r="B62" s="0" t="s">
+      <c r="A62" s="5"/>
+      <c r="B62" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="3" t="n">
         <v>150000000</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="4" t="n">
         <v>46864</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" s="3" t="n">
+      <c r="F62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="4" t="n">
         <v>46134</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4"/>
-      <c r="C63" s="5" t="s">
+      <c r="A63" s="5"/>
+      <c r="C63" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="7" t="n">
         <f aca="false">SUM(D62)</f>
         <v>150000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4"/>
-      <c r="B65" s="0" t="s">
+      <c r="A65" s="5"/>
+      <c r="B65" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="3" t="n">
         <v>180000000</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="4" t="n">
         <v>46415</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="3" t="n">
+      <c r="F65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="4" t="n">
         <v>46051</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4"/>
-      <c r="B66" s="0" t="s">
+      <c r="A66" s="5"/>
+      <c r="B66" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="3" t="n">
         <v>100480770</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="4" t="n">
         <v>46373</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="3" t="n">
+      <c r="F66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="4" t="n">
         <v>46142</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4"/>
-      <c r="B67" s="0" t="s">
+      <c r="A67" s="5"/>
+      <c r="B67" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>105000000</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="4" t="n">
         <v>46534</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="3" t="n">
+      <c r="F67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="4" t="n">
         <v>46172</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4"/>
-      <c r="B68" s="0" t="s">
+      <c r="A68" s="5"/>
+      <c r="B68" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="3" t="n">
         <v>120000000</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="4" t="n">
         <v>46415</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" s="3" t="n">
+      <c r="F68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="4" t="n">
         <v>46051</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4"/>
-      <c r="B69" s="0" t="s">
+      <c r="A69" s="5"/>
+      <c r="B69" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="4" t="n">
         <v>46197</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="3" t="n">
+      <c r="F69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="4" t="n">
         <v>46183</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4"/>
-      <c r="B70" s="0" t="s">
+      <c r="A70" s="5"/>
+      <c r="B70" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D70" s="3" t="n">
         <v>100480770</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="4" t="n">
         <v>46373</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G70" s="3" t="n">
+      <c r="F70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="4" t="n">
         <v>46142</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4"/>
-      <c r="B71" s="0" t="s">
+      <c r="A71" s="5"/>
+      <c r="B71" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="4" t="n">
         <v>46197</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G71" s="3" t="n">
+      <c r="F71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="4" t="n">
         <v>46183</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4"/>
-      <c r="B72" s="0" t="s">
+      <c r="A72" s="5"/>
+      <c r="B72" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" s="3" t="n">
         <v>50000000</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" s="3" t="n">
+      <c r="F72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="4" t="n">
         <v>46122</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4"/>
-      <c r="B73" s="8" t="s">
+      <c r="A73" s="5"/>
+      <c r="B73" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="3" t="n">
         <v>50000000</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="3" t="n">
+      <c r="F73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="4" t="n">
         <v>46122</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4"/>
-      <c r="B74" s="0" t="s">
+      <c r="A74" s="5"/>
+      <c r="B74" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="3" t="n">
         <v>70000000</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="4" t="n">
         <v>46534</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G74" s="3" t="n">
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="4" t="n">
         <v>46170</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4"/>
-      <c r="C75" s="5" t="s">
+      <c r="A75" s="5"/>
+      <c r="C75" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="7" t="n">
         <f aca="false">SUM(D65:D74)</f>
         <v>925961540</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4"/>
-      <c r="B77" s="0" t="s">
+      <c r="A77" s="5"/>
+      <c r="B77" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="3" t="n">
         <v>164705883</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="4" t="n">
         <v>46360</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G77" s="3" t="n">
+      <c r="F77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="4" t="n">
         <v>45996</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4"/>
-      <c r="B78" s="0" t="s">
+      <c r="A78" s="5"/>
+      <c r="B78" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="3" t="n">
         <v>300000000</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="4" t="n">
         <v>46479</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="3" t="n">
+      <c r="F78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="4" t="n">
         <v>46158</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4"/>
-      <c r="C79" s="5" t="s">
+      <c r="A79" s="5"/>
+      <c r="C79" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="7" t="n">
         <f aca="false">SUM(D76:D77)</f>
         <v>164705883</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4"/>
-      <c r="B81" s="0" t="s">
+      <c r="A81" s="5"/>
+      <c r="B81" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="4" t="n">
         <v>46528</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G81" s="3" t="n">
+      <c r="F81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="4" t="n">
         <v>46168</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4"/>
-      <c r="B82" s="0" t="s">
+      <c r="A82" s="5"/>
+      <c r="B82" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="3" t="n">
         <v>75000000</v>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="4" t="n">
         <v>46346</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G82" s="3" t="n">
+      <c r="F82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="4" t="n">
         <v>45987</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4"/>
-      <c r="C83" s="5" t="s">
+      <c r="A83" s="5"/>
+      <c r="C83" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="7" t="n">
         <f aca="false">SUM(D81:D82)</f>
         <v>150000000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="5" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4"/>
-      <c r="B85" s="0" t="s">
+      <c r="A85" s="5"/>
+      <c r="B85" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="3" t="n">
         <v>125000000</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="4" t="n">
         <v>46309</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G85" s="3" t="n">
+      <c r="F85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" s="4" t="n">
         <v>45965</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4"/>
-      <c r="C86" s="5" t="s">
+      <c r="A86" s="5"/>
+      <c r="C86" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="7" t="n">
         <f aca="false">SUM(D85)</f>
         <v>125000000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="5" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="3" t="n">
         <v>240119760</v>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="4" t="n">
         <v>46927</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G88" s="3" t="n">
+      <c r="F88" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="4" t="n">
         <v>46162</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="3" t="n">
         <v>59880330</v>
       </c>
-      <c r="E89" s="3" t="n">
+      <c r="E89" s="4" t="n">
         <v>46927</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="3" t="n">
+      <c r="F89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="4" t="n">
         <v>46162</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" s="3" t="n">
         <v>400000000</v>
       </c>
-      <c r="E90" s="3" t="n">
+      <c r="E90" s="4" t="n">
         <v>46486</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G90" s="3" t="n">
+      <c r="F90" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="4" t="n">
         <v>46143</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" s="3" t="n">
         <v>27376000</v>
       </c>
-      <c r="E91" s="3" t="n">
+      <c r="E91" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G91" s="3" t="n">
+      <c r="F91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="4" t="n">
         <v>45945</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D92" s="3" t="n">
         <v>135000000</v>
       </c>
-      <c r="E92" s="3" t="n">
+      <c r="E92" s="4" t="n">
         <v>47242</v>
       </c>
-      <c r="F92" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" s="3" t="n">
+      <c r="F92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="4" t="n">
         <v>46151</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" s="3" t="n">
         <v>132134434</v>
       </c>
-      <c r="E93" s="3" t="n">
+      <c r="E93" s="4" t="n">
         <v>46843</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="3" t="n">
+      <c r="F93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="4" t="n">
         <v>46112</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="3" t="n">
         <v>300000000</v>
       </c>
-      <c r="E94" s="3" t="n">
+      <c r="E94" s="4" t="n">
         <v>46738</v>
       </c>
-      <c r="F94" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="3" t="n">
+      <c r="F94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="4" t="n">
         <v>46015</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D95" s="3" t="n">
         <v>150000000</v>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="E95" s="4" t="n">
         <v>46542</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" s="3" t="n">
+      <c r="F95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="4" t="n">
         <v>46179</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D96" s="2" t="n">
+      <c r="D96" s="3" t="n">
         <v>230000000</v>
       </c>
-      <c r="E96" s="3" t="n">
+      <c r="E96" s="4" t="n">
         <v>46864</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3" t="n">
+      <c r="F96" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="4" t="n">
         <v>46142</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D97" s="2" t="n">
+      <c r="D97" s="3" t="n">
         <v>215000000</v>
       </c>
-      <c r="E97" s="3" t="n">
+      <c r="E97" s="4" t="n">
         <v>46262</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" s="3" t="n">
+      <c r="F97" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" s="4" t="n">
         <v>46044</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D98" s="3" t="n">
         <v>245714285</v>
       </c>
-      <c r="E98" s="3" t="n">
+      <c r="E98" s="4" t="n">
         <v>46752</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" s="3" t="n">
+      <c r="F98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" s="4" t="n">
         <v>46051</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D99" s="3" t="n">
         <v>273000000</v>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="E99" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" s="3" t="n">
+      <c r="F99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="4" t="n">
         <v>45839</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D100" s="2" t="n">
+      <c r="D100" s="3" t="n">
         <v>200000000</v>
       </c>
-      <c r="E100" s="3" t="n">
+      <c r="E100" s="4" t="n">
         <v>46280</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" s="3" t="n">
+      <c r="F100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="4" t="n">
         <v>46071</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D101" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="E101" s="3" t="n">
+      <c r="E101" s="4" t="n">
         <v>46430</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" s="3" t="n">
+      <c r="F101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="4" t="n">
         <v>46126</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D102" s="3" t="n">
         <v>150000000</v>
       </c>
-      <c r="E102" s="3" t="n">
+      <c r="E102" s="4" t="n">
         <v>46542</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G102" s="3" t="n">
+      <c r="F102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" s="4" t="n">
         <v>46178</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D103" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="E103" s="3" t="n">
+      <c r="E103" s="4" t="n">
         <v>46513</v>
       </c>
-      <c r="F103" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G103" s="3" t="n">
+      <c r="F103" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G103" s="4" t="n">
         <v>46153</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C104" s="5" t="s">
+      <c r="C104" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="7" t="n">
         <f aca="false">SUM(D88:D103)</f>
         <v>3183224809</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C105" s="5" t="s">
+      <c r="C105" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="7" t="n">
         <v>10555217539</v>
       </c>
     </row>
@@ -2369,4 +3043,602 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="69.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="45.88"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D23" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D24" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D25" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C41" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C42" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C44" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C46" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D47" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D48" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D49" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D50" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C53" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C54" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D55" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D56" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D57" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D58" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D59" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D60" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D61" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D62" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C65" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C66" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C67" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C68" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C69" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C70" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C71" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D72" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D73" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D74" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D75" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D76" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D77" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D78" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D79" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D80" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D81" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>